--- a/backend/global_members.xlsx
+++ b/backend/global_members.xlsx
@@ -118,10 +118,10 @@
     <t>West Nyack</t>
   </si>
   <si>
-    <t>ajay.avasatthi</t>
-  </si>
-  <si>
     <t xml:space="preserve"> LEN-GG45AA</t>
+  </si>
+  <si>
+    <t>ajay11</t>
   </si>
 </sst>
 </file>
@@ -606,16 +606,16 @@
         <v>22</v>
       </c>
       <c r="S2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" t="s">
         <v>35</v>
-      </c>
-      <c r="T2" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:U1 A2:Q2 T2:U2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:U1 A2:Q2 U2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/global_members.xlsx
+++ b/backend/global_members.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>firstName</t>
   </si>
@@ -493,7 +493,8 @@
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="18" max="18" width="12.375" customWidth="1"/>
+    <col min="17" max="17" width="63" customWidth="1"/>
+    <col min="18" max="18" width="18.25" customWidth="1"/>
     <col min="19" max="19" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -604,6 +605,9 @@
       </c>
       <c r="Q2" t="s">
         <v>22</v>
+      </c>
+      <c r="R2" t="s">
+        <v>34</v>
       </c>
       <c r="S2" t="s">
         <v>34</v>

--- a/backend/global_members.xlsx
+++ b/backend/global_members.xlsx
@@ -1,43 +1,245 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView xWindow="615" yWindow="570" windowWidth="21795" windowHeight="8670"/>
+  </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="70">
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>spouseName</t>
+  </si>
+  <si>
+    <t>degree</t>
+  </si>
+  <si>
+    <t>branch</t>
+  </si>
+  <si>
+    <t>graduationYear</t>
+  </si>
+  <si>
+    <t>profession</t>
+  </si>
+  <si>
+    <t>mobileNumber</t>
+  </si>
+  <si>
+    <t>EmailAddress</t>
+  </si>
+  <si>
+    <t>EmployerBusinessName</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>NativeLocation</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>memberCode</t>
+  </si>
+  <si>
+    <t>recommenderCode</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>dob</t>
+  </si>
+  <si>
+    <t>mastersBranch</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>Babulal</t>
+  </si>
+  <si>
+    <t>Vaghani</t>
+  </si>
+  <si>
+    <t>Sarala</t>
+  </si>
+  <si>
+    <t>Degree</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>Business</t>
+  </si>
+  <si>
+    <t>224-716-4060</t>
+  </si>
+  <si>
+    <t>Babulalvaghani4@gmail.com</t>
+  </si>
+  <si>
+    <t>Liquor store</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>Fort Worth</t>
+  </si>
+  <si>
+    <t>Kumbhan -Palitana-Bhavnagar</t>
+  </si>
+  <si>
+    <t>$2a$10$OfQ6idSEkiWdA1KXu0wFyONIv7ytWe6kqbt4bfQqqByumCw8KOYFC</t>
+  </si>
+  <si>
+    <t>LEN-A9F27V</t>
+  </si>
+  <si>
+    <t>LEN-KHTUN8</t>
+  </si>
+  <si>
+    <t>babulal11</t>
+  </si>
+  <si>
+    <t>Bakul</t>
+  </si>
+  <si>
+    <t>Viradia</t>
+  </si>
+  <si>
+    <t>Lata</t>
+  </si>
+  <si>
+    <t>Civil</t>
+  </si>
+  <si>
+    <t>VoIP Enginner</t>
+  </si>
+  <si>
+    <t>301-821-5814</t>
+  </si>
+  <si>
+    <t>bdviradia@yahoo.com</t>
+  </si>
+  <si>
+    <t>US Dept. of Labor</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Amreli, Saurashtra</t>
+  </si>
+  <si>
+    <t>LEN-QUDG9N</t>
+  </si>
+  <si>
+    <t>LEN-A2HNGF</t>
+  </si>
+  <si>
+    <t>bakul11</t>
+  </si>
+  <si>
+    <t>Chunilal</t>
+  </si>
+  <si>
+    <t>Bhut</t>
+  </si>
+  <si>
+    <t>AAAA</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1968</t>
+  </si>
+  <si>
+    <t>Retired</t>
+  </si>
+  <si>
+    <t>9042078666</t>
+  </si>
+  <si>
+    <t>16016cs@gmail.com</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>St. Johns</t>
+  </si>
+  <si>
+    <t>RAJKOT</t>
+  </si>
+  <si>
+    <t>$2b$10$hjxB6EVbtksYHWKaRvP/.eqosZ4Nhp3h3oa4y4fLUIdxY.T/ZsmB2</t>
+  </si>
+  <si>
+    <t>LEN-5824PB</t>
+  </si>
+  <si>
+    <t>csbhut11</t>
+  </si>
+  <si>
+    <t>production &amp; Industrial</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>Mechancal</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,8 +266,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,324 +603,259 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:U4"/>
+  <sheetFormatPr defaultColWidth="13.375" defaultRowHeight="21"/>
+  <cols>
+    <col min="1" max="16384" width="13.375" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>firstName</v>
-      </c>
-      <c r="B1" t="str">
-        <v>lastName</v>
-      </c>
-      <c r="C1" t="str">
-        <v>spouseName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>degree</v>
-      </c>
-      <c r="E1" t="str">
-        <v>branch</v>
-      </c>
-      <c r="F1" t="str">
-        <v>graduationYear</v>
-      </c>
-      <c r="G1" t="str">
-        <v>profession</v>
-      </c>
-      <c r="H1" t="str">
-        <v>mobileNumber</v>
-      </c>
-      <c r="I1" t="str">
-        <v>EmailAddress</v>
-      </c>
-      <c r="J1" t="str">
-        <v>EmployerBusinessName</v>
-      </c>
-      <c r="K1" t="str">
-        <v>country</v>
-      </c>
-      <c r="L1" t="str">
-        <v>state</v>
-      </c>
-      <c r="M1" t="str">
-        <v>city</v>
-      </c>
-      <c r="N1" t="str">
-        <v>NativeLocation</v>
-      </c>
-      <c r="O1" t="str">
-        <v>password</v>
-      </c>
-      <c r="P1" t="str">
-        <v>memberCode</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>recommenderCode</v>
-      </c>
-      <c r="R1" t="str">
-        <v>username</v>
-      </c>
-      <c r="S1" t="str">
-        <v>dob</v>
-      </c>
-      <c r="T1" t="str">
-        <v>mastersBranch</v>
-      </c>
-      <c r="U1" t="str">
-        <v>date</v>
-      </c>
-      <c r="V1" t="str">
-        <v>email</v>
+    <row r="1" spans="1:21">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Babulal</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Vaghani</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Sarala</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Degree</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Mechanical</v>
-      </c>
-      <c r="F2">
+    <row r="2" spans="1:21">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="1">
         <v>1973</v>
       </c>
-      <c r="G2" t="str">
-        <v>Business</v>
-      </c>
-      <c r="H2" t="str">
-        <v>224-716-4060</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Babulalvaghani4@gmail.com</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Liquor store</v>
-      </c>
-      <c r="K2" t="str">
-        <v>USA</v>
-      </c>
-      <c r="L2" t="str">
-        <v>TX</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Fort Worth</v>
-      </c>
-      <c r="N2" t="str">
-        <v>Kumbhan -Palitana-Bhavnagar</v>
-      </c>
-      <c r="O2" t="str">
-        <v>$2a$10$OfQ6idSEkiWdA1KXu0wFyONIv7ytWe6kqbt4bfQqqByumCw8KOYFC</v>
-      </c>
-      <c r="P2" t="str">
-        <v>LEN-A9F27V</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>LEN-KHTUN8</v>
-      </c>
-      <c r="R2" t="str">
-        <v>babulal11</v>
+      <c r="G2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Bakul</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Viradia</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Lata</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Degree</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Civil</v>
-      </c>
-      <c r="F3">
+    <row r="3" spans="1:21">
+      <c r="A3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="1">
         <v>1988</v>
       </c>
-      <c r="G3" t="str">
-        <v>VoIP Enginner</v>
-      </c>
-      <c r="H3" t="str">
-        <v>301-821-5814</v>
-      </c>
-      <c r="I3" t="str">
-        <v>bdviradia@yahoo.com</v>
-      </c>
-      <c r="J3" t="str">
-        <v>US Dept. of Labor</v>
-      </c>
-      <c r="K3" t="str">
-        <v>USA</v>
-      </c>
-      <c r="L3" t="str">
-        <v>DC</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Washington</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Amreli, Saurashtra</v>
-      </c>
-      <c r="O3" t="str">
-        <v>$2a$10$OfQ6idSEkiWdA1KXu0wFyONIv7ytWe6kqbt4bfQqqByumCw8KOYFC</v>
-      </c>
-      <c r="P3" t="str">
-        <v>LEN-QUDG9N</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>LEN-A2HNGF</v>
-      </c>
-      <c r="R3" t="str">
-        <v>bakul11</v>
+      <c r="G3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>CHUNILAL</v>
-      </c>
-      <c r="B4" t="str">
-        <v>BHUT</v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v>9042078666</v>
-      </c>
-      <c r="I4" t="str">
-        <v>16016cs@gmail.com</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v>USA</v>
-      </c>
-      <c r="L4" t="str">
-        <v>FL</v>
-      </c>
-      <c r="M4" t="str">
-        <v>St. Johns</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v>$2b$10$z6G8Sp1JZ.WObJbKrWT1/uRwTjS2sR2r56gTvVBzUo44lEbRu9nbm</v>
-      </c>
-      <c r="P4" t="str">
-        <v>LEN-ZU84VX</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>LEN-A9F27V</v>
-      </c>
-      <c r="R4" t="str">
-        <v>csbhut11</v>
-      </c>
-      <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <v/>
-      </c>
-      <c r="U4" t="str">
-        <v>08/01/2026</v>
-      </c>
-      <c r="V4" t="str">
-        <v>16016cs@gmail.com</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>CHUNILAL</v>
-      </c>
-      <c r="B5" t="str">
-        <v>BHUT</v>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v>9042078666</v>
-      </c>
-      <c r="I5" t="str">
-        <v>16016cs@gmail.com</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v>USA</v>
-      </c>
-      <c r="L5" t="str">
-        <v>FL</v>
-      </c>
-      <c r="M5" t="str">
-        <v>St. Johns</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v>$2b$10$ZqUJJLSV0i6bWzISg9Uq7eyg/WEhrhuRtqQYywxLVuNbV6o35U9W.</v>
-      </c>
-      <c r="P5" t="str">
-        <v>LEN-WMSEMN</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>LEN-A9F27V</v>
-      </c>
-      <c r="R5" t="str">
-        <v>csbhut1111</v>
-      </c>
-      <c r="S5" t="str">
-        <v/>
-      </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-      <c r="U5" t="str">
-        <v>08/01/2026</v>
+    <row r="4" spans="1:21">
+      <c r="A4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V5"/>
+    <ignoredError sqref="A2:U3 A4:D4 F4:U4 A1:M1 O1:U1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>